--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.00845820783045732</v>
       </c>
       <c r="C2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>43890292</v>
+        <v>4065217</v>
       </c>
       <c r="L2" t="n">
-        <v>23587089</v>
+        <v>1731438</v>
       </c>
       <c r="M2" t="n">
-        <v>5372937</v>
+        <v>300236</v>
       </c>
       <c r="N2" t="n">
-        <v>239758</v>
+        <v>6066</v>
       </c>
       <c r="O2" t="n">
-        <v>3160004</v>
+        <v>157246</v>
       </c>
       <c r="P2" t="n">
-        <v>1204362</v>
+        <v>58949</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999271631240845</v>
+        <v>0.9996204376220703</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8442781567573547</v>
+        <v>0.7276571989059448</v>
       </c>
       <c r="S2" t="n">
-        <v>0.716714084148407</v>
+        <v>0.5488982200622559</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6567645072937012</v>
+        <v>0.4240645468235016</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2172073125839233</v>
+        <v>0.04493067041039467</v>
       </c>
       <c r="V2" t="n">
-        <v>0.702092707157135</v>
+        <v>0.4706737995147705</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8135256171226501</v>
+        <v>0.6138858199119568</v>
       </c>
       <c r="X2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>47949558</v>
+        <v>4750163</v>
       </c>
       <c r="AG2" t="n">
-        <v>29849211</v>
+        <v>3018205</v>
       </c>
       <c r="AH2" t="n">
-        <v>8017135</v>
+        <v>806591</v>
       </c>
       <c r="AI2" t="n">
-        <v>590732</v>
+        <v>59281</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559409618377686</v>
+        <v>0.9546809196472168</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116660952568054</v>
+        <v>0.9128581881523132</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582287430763245</v>
+        <v>0.8581860065460205</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6617533564567566</v>
+        <v>0.6609027981758118</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.902009129524231</v>
+        <v>0.901951789855957</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002027664927559576</v>
       </c>
       <c r="C3" t="n">
-        <v>500</v>
+        <v>261</v>
       </c>
       <c r="D3" t="n">
-        <v>43890292</v>
+        <v>4065217</v>
       </c>
       <c r="E3" t="n">
-        <v>6014500</v>
+        <v>861138</v>
       </c>
       <c r="F3" t="n">
-        <v>147089</v>
+        <v>28567</v>
       </c>
       <c r="G3" t="n">
-        <v>14237</v>
+        <v>2822</v>
       </c>
       <c r="H3" t="n">
-        <v>8419</v>
+        <v>1835</v>
       </c>
       <c r="I3" t="n">
-        <v>703</v>
+        <v>272</v>
       </c>
       <c r="J3" t="n">
-        <v>100161621</v>
+        <v>10014225</v>
       </c>
       <c r="K3" t="n">
-        <v>105124970</v>
+        <v>9847985</v>
       </c>
       <c r="L3" t="n">
-        <v>121163729</v>
+        <v>11587518</v>
       </c>
       <c r="M3" t="n">
-        <v>151135465</v>
+        <v>14979984</v>
       </c>
       <c r="N3" t="n">
-        <v>161538373</v>
+        <v>16110850</v>
       </c>
       <c r="O3" t="n">
-        <v>156854738</v>
+        <v>15640850</v>
       </c>
       <c r="P3" t="n">
-        <v>161085326</v>
+        <v>16098718</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8764781355857849</v>
+        <v>0.8195816874504089</v>
       </c>
       <c r="S3" t="n">
-        <v>0.718914270401001</v>
+        <v>0.5216538310050964</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5744888186454773</v>
+        <v>0.3187705874443054</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2683165371417999</v>
+        <v>0.06754409521818161</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6195563673973083</v>
+        <v>0.3071756958961487</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6225337982177734</v>
+        <v>0.3041665554046631</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>47949558</v>
+        <v>4750163</v>
       </c>
       <c r="Z3" t="n">
-        <v>1972670</v>
+        <v>194702</v>
       </c>
       <c r="AA3" t="n">
-        <v>84826</v>
+        <v>8398</v>
       </c>
       <c r="AB3" t="n">
-        <v>68106</v>
+        <v>6808</v>
       </c>
       <c r="AC3" t="n">
-        <v>280</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100166220</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>111010280</v>
+        <v>11143996</v>
       </c>
       <c r="AG3" t="n">
-        <v>127594505</v>
+        <v>12722349</v>
       </c>
       <c r="AH3" t="n">
-        <v>152619092</v>
+        <v>15254456</v>
       </c>
       <c r="AI3" t="n">
-        <v>162100491</v>
+        <v>16209376</v>
       </c>
       <c r="AJ3" t="n">
-        <v>157696105</v>
+        <v>15767551</v>
       </c>
       <c r="AK3" t="n">
-        <v>161228809</v>
+        <v>16122526</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575406908988953</v>
+        <v>0.9576725363731384</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097784161567688</v>
+        <v>0.9093356132507324</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85721355676651</v>
+        <v>0.8563846349716187</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.661096453666687</v>
+        <v>0.6600859761238098</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014128446578979</v>
+        <v>0.9010214805603027</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03198836053224347</v>
       </c>
       <c r="C4" t="n">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="D4" t="n">
-        <v>7499597</v>
+        <v>1368937</v>
       </c>
       <c r="E4" t="n">
-        <v>23587089</v>
+        <v>1731438</v>
       </c>
       <c r="F4" t="n">
-        <v>1459680</v>
+        <v>173092</v>
       </c>
       <c r="G4" t="n">
-        <v>102350</v>
+        <v>17643</v>
       </c>
       <c r="H4" t="n">
-        <v>145326</v>
+        <v>24126</v>
       </c>
       <c r="I4" t="n">
-        <v>15088</v>
+        <v>3761</v>
       </c>
       <c r="J4" t="n">
-        <v>4599</v>
+        <v>2397</v>
       </c>
       <c r="K4" t="n">
-        <v>8095290</v>
+        <v>1521503</v>
       </c>
       <c r="L4" t="n">
-        <v>9322951</v>
+        <v>1422950</v>
       </c>
       <c r="M4" t="n">
-        <v>2807982</v>
+        <v>407760</v>
       </c>
       <c r="N4" t="n">
-        <v>864063</v>
+        <v>128942</v>
       </c>
       <c r="O4" t="n">
-        <v>1340832</v>
+        <v>176841</v>
       </c>
       <c r="P4" t="n">
-        <v>276061</v>
+        <v>37077</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999635815620422</v>
+        <v>0.9998101592063904</v>
       </c>
       <c r="R4" t="n">
-        <v>0.860076904296875</v>
+        <v>0.7708887457847595</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7178124785423279</v>
+        <v>0.5349293351173401</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6128776669502258</v>
+        <v>0.3639550805091858</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2400718927383423</v>
+        <v>0.05396412685513496</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6582473516464233</v>
+        <v>0.3717416822910309</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7053290009498596</v>
+        <v>0.4067818820476532</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2063963</v>
+        <v>210743</v>
       </c>
       <c r="Z4" t="n">
-        <v>29849211</v>
+        <v>3018205</v>
       </c>
       <c r="AA4" t="n">
-        <v>828823</v>
+        <v>83377</v>
       </c>
       <c r="AB4" t="n">
-        <v>55262</v>
+        <v>5608</v>
       </c>
       <c r="AC4" t="n">
-        <v>11381</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2209980</v>
+        <v>225492</v>
       </c>
       <c r="AG4" t="n">
-        <v>2892175</v>
+        <v>288119</v>
       </c>
       <c r="AH4" t="n">
-        <v>1324355</v>
+        <v>133288</v>
       </c>
       <c r="AI4" t="n">
-        <v>301945</v>
+        <v>30416</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499465</v>
+        <v>50140</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567400813102722</v>
+        <v>0.956174373626709</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107212424278259</v>
+        <v>0.9110934734344482</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577207922935486</v>
+        <v>0.8572843670845032</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614247560501099</v>
+        <v>0.6604941487312317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017109274864197</v>
+        <v>0.9014863967895508</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>687</v>
+        <v>409</v>
       </c>
       <c r="D5" t="n">
-        <v>422677</v>
+        <v>113000</v>
       </c>
       <c r="E5" t="n">
-        <v>2690128</v>
+        <v>425095</v>
       </c>
       <c r="F5" t="n">
-        <v>5372937</v>
+        <v>300236</v>
       </c>
       <c r="G5" t="n">
-        <v>265178</v>
+        <v>33196</v>
       </c>
       <c r="H5" t="n">
-        <v>542998</v>
+        <v>59190</v>
       </c>
       <c r="I5" t="n">
-        <v>57948</v>
+        <v>10730</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6185448</v>
+        <v>894895</v>
       </c>
       <c r="L5" t="n">
-        <v>9222231</v>
+        <v>1587694</v>
       </c>
       <c r="M5" t="n">
-        <v>3979616</v>
+        <v>641620</v>
       </c>
       <c r="N5" t="n">
-        <v>653806</v>
+        <v>83742</v>
       </c>
       <c r="O5" t="n">
-        <v>1940426</v>
+        <v>354663</v>
       </c>
       <c r="P5" t="n">
-        <v>730251</v>
+        <v>134856</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999718070030212</v>
+        <v>0.9998531937599182</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9125469326972961</v>
+        <v>0.8520234227180481</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8864321112632751</v>
+        <v>0.815632700920105</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9584337472915649</v>
+        <v>0.9357375502586365</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9907047748565674</v>
+        <v>0.9869755506515503</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9799060821533203</v>
+        <v>0.9674515128135681</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9938374757766724</v>
+        <v>0.9894710779190063</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80454</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>857060</v>
+        <v>87176</v>
       </c>
       <c r="AA5" t="n">
-        <v>8017135</v>
+        <v>806591</v>
       </c>
       <c r="AB5" t="n">
-        <v>99758</v>
+        <v>10039</v>
       </c>
       <c r="AC5" t="n">
-        <v>291816</v>
+        <v>29297</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2126182</v>
+        <v>209949</v>
       </c>
       <c r="AG5" t="n">
-        <v>2960109</v>
+        <v>300927</v>
       </c>
       <c r="AH5" t="n">
-        <v>1335418</v>
+        <v>135265</v>
       </c>
       <c r="AI5" t="n">
-        <v>302832</v>
+        <v>30527</v>
       </c>
       <c r="AJ5" t="n">
-        <v>502837</v>
+        <v>50668</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734460115432739</v>
+        <v>0.9733342528343201</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641615152359009</v>
+        <v>0.963927686214447</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837119579315186</v>
+        <v>0.9835542440414429</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962964653968811</v>
+        <v>0.9962679147720337</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938620328903198</v>
+        <v>0.993826687335968</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983729124069214</v>
+        <v>0.9983675479888916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="D6" t="n">
-        <v>135317</v>
+        <v>23082</v>
       </c>
       <c r="E6" t="n">
-        <v>222567</v>
+        <v>27421</v>
       </c>
       <c r="F6" t="n">
-        <v>206492</v>
+        <v>25307</v>
       </c>
       <c r="G6" t="n">
-        <v>239758</v>
+        <v>6066</v>
       </c>
       <c r="H6" t="n">
-        <v>81109</v>
+        <v>6754</v>
       </c>
       <c r="I6" t="n">
-        <v>8190</v>
+        <v>1119</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65084</v>
+        <v>6593</v>
       </c>
       <c r="Z6" t="n">
-        <v>53535</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>109471</v>
+        <v>11081</v>
       </c>
       <c r="AB6" t="n">
-        <v>590732</v>
+        <v>59281</v>
       </c>
       <c r="AC6" t="n">
-        <v>69932</v>
+        <v>7022</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1026</v>
+        <v>575</v>
       </c>
       <c r="D7" t="n">
-        <v>35383</v>
+        <v>15108</v>
       </c>
       <c r="E7" t="n">
-        <v>362969</v>
+        <v>98382</v>
       </c>
       <c r="F7" t="n">
-        <v>919004</v>
+        <v>158359</v>
       </c>
       <c r="G7" t="n">
-        <v>427912</v>
+        <v>61044</v>
       </c>
       <c r="H7" t="n">
-        <v>3160004</v>
+        <v>157246</v>
       </c>
       <c r="I7" t="n">
-        <v>194132</v>
+        <v>21195</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8100</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>297921</v>
+        <v>30099</v>
       </c>
       <c r="AB7" t="n">
-        <v>76159</v>
+        <v>7694</v>
       </c>
       <c r="AC7" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2065</v>
+        <v>958</v>
       </c>
       <c r="D8" t="n">
-        <v>2316</v>
+        <v>1376</v>
       </c>
       <c r="E8" t="n">
-        <v>32787</v>
+        <v>10914</v>
       </c>
       <c r="F8" t="n">
-        <v>75717</v>
+        <v>22435</v>
       </c>
       <c r="G8" t="n">
-        <v>54386</v>
+        <v>14237</v>
       </c>
       <c r="H8" t="n">
-        <v>562980</v>
+        <v>84936</v>
       </c>
       <c r="I8" t="n">
-        <v>1204362</v>
+        <v>58949</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
